--- a/output/yearly_benthic_cover_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_90_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.67296962392705</v>
+        <v>45.42940953923235</v>
       </c>
       <c r="M2" t="n">
-        <v>98.90296274207509</v>
+        <v>98.9652998830841</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0621850870365</v>
+        <v>88.00920016343832</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94152453789798</v>
+        <v>45.88900246743617</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228810313257875</v>
+        <v>2.228714254844044</v>
       </c>
       <c r="E3" t="n">
-        <v>5.71559855476638</v>
+        <v>5.682813365944683</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429367710859586</v>
+        <v>0.7429047516146814</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9772142345801</v>
+        <v>33.9595151024918</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17509146995409</v>
+        <v>34.17361857427534</v>
       </c>
       <c r="I3" t="n">
-        <v>6.579178924104858</v>
+        <v>6.578479416676012</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643354819287241</v>
+        <v>4.643154697591758</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93781491296349</v>
+        <v>11.99079983656169</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88451020884375</v>
+        <v>48.88406228645368</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7638496597052</v>
+        <v>106.7638645904515</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.2216798971122</v>
+        <v>87.15301538162967</v>
       </c>
       <c r="C4" t="n">
-        <v>42.73782953433611</v>
+        <v>42.67144038984712</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188709896474705</v>
+        <v>2.187728257673261</v>
       </c>
       <c r="E4" t="n">
-        <v>6.528457869987379</v>
+        <v>6.493904024940663</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444967097859174</v>
+        <v>0.7444656883015559</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36590135441573</v>
+        <v>33.33500050314974</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2468486501522</v>
+        <v>34.24542166187157</v>
       </c>
       <c r="I4" t="n">
-        <v>5.494160980134287</v>
+        <v>5.493584693808167</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653104436161984</v>
+        <v>4.652910551884724</v>
       </c>
       <c r="K4" t="n">
-        <v>12.77832010288781</v>
+        <v>12.84698461837034</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30109539266204</v>
+        <v>44.29883945243044</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81724502988597</v>
+        <v>99.81726446064789</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.18348875827138</v>
+        <v>86.08332369625988</v>
       </c>
       <c r="C5" t="n">
-        <v>42.55245260573047</v>
+        <v>42.45440466283544</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138501232640703</v>
+        <v>2.135817548103723</v>
       </c>
       <c r="E5" t="n">
-        <v>7.143127650016237</v>
+        <v>7.104168638577063</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458174193759632</v>
+        <v>0.7457877433484599</v>
       </c>
       <c r="G5" t="n">
-        <v>32.60049277865125</v>
+        <v>32.54402313950778</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3076012912943</v>
+        <v>34.30623619402915</v>
       </c>
       <c r="I5" t="n">
-        <v>4.586589515193154</v>
+        <v>4.586117036765822</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66135887109977</v>
+        <v>4.661173395927873</v>
       </c>
       <c r="K5" t="n">
-        <v>13.81651124172862</v>
+        <v>13.91667630374014</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47842056975941</v>
+        <v>43.47631945859643</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84738441721851</v>
+        <v>99.847400425172</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.88069472239997</v>
+        <v>84.81331790811886</v>
       </c>
       <c r="C6" t="n">
-        <v>41.96217136636734</v>
+        <v>41.89675198094682</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075095267938871</v>
+        <v>2.074015587326144</v>
       </c>
       <c r="E6" t="n">
-        <v>7.569319839292746</v>
+        <v>7.536521473209894</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746938568372667</v>
+        <v>0.7469096239405664</v>
       </c>
       <c r="G6" t="n">
-        <v>31.63389726641346</v>
+        <v>31.60233013609642</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35917414514268</v>
+        <v>34.35784270126604</v>
       </c>
       <c r="I6" t="n">
-        <v>3.827903582910371</v>
+        <v>3.827513236651239</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668366052329169</v>
+        <v>4.668185149628539</v>
       </c>
       <c r="K6" t="n">
-        <v>15.11930527760004</v>
+        <v>15.18668209188114</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79111809172171</v>
+        <v>42.78917378726187</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87259473568908</v>
+        <v>99.87260786008984</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.40241252090145</v>
+        <v>83.33883516321038</v>
       </c>
       <c r="C7" t="n">
-        <v>41.07862201592343</v>
+        <v>41.01689313631054</v>
       </c>
       <c r="D7" t="n">
-        <v>2.00333485965569</v>
+        <v>2.002367556108172</v>
       </c>
       <c r="E7" t="n">
-        <v>7.839891528047729</v>
+        <v>7.808446230048879</v>
       </c>
       <c r="F7" t="n">
-        <v>0.74789206420946</v>
+        <v>0.747863713704163</v>
       </c>
       <c r="G7" t="n">
-        <v>30.53994200638301</v>
+        <v>30.51060992435451</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40303495363516</v>
+        <v>34.40173083039149</v>
       </c>
       <c r="I7" t="n">
-        <v>3.193991707661282</v>
+        <v>3.193668697952149</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674325401309125</v>
+        <v>4.674148210651018</v>
       </c>
       <c r="K7" t="n">
-        <v>16.59758747909856</v>
+        <v>16.66116483678963</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21745984989716</v>
+        <v>42.21562221477062</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89366934491915</v>
+        <v>99.89368018787079</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.18543363551983</v>
+        <v>88.23931996549028</v>
       </c>
       <c r="C8" t="n">
-        <v>43.28409638018353</v>
+        <v>43.31255300940229</v>
       </c>
       <c r="D8" t="n">
-        <v>2.007611875420846</v>
+        <v>2.006659674129188</v>
       </c>
       <c r="E8" t="n">
-        <v>9.608836509513074</v>
+        <v>9.639137992580386</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494887748810891</v>
+        <v>0.7494667756959847</v>
       </c>
       <c r="G8" t="n">
-        <v>31.01056851565248</v>
+        <v>31.01012995804944</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4764836445301</v>
+        <v>34.47547168201529</v>
       </c>
       <c r="I8" t="n">
-        <v>5.648139472515425</v>
+        <v>5.674286534920084</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684304843006807</v>
+        <v>4.684167348099904</v>
       </c>
       <c r="K8" t="n">
-        <v>11.81456636448019</v>
+        <v>11.7606800345097</v>
       </c>
       <c r="L8" t="n">
-        <v>44.713467032743</v>
+        <v>44.73802863624784</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81212977740671</v>
+        <v>99.81126168015984</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.28873028229563</v>
+        <v>86.398026150996</v>
       </c>
       <c r="C9" t="n">
-        <v>42.26426613787046</v>
+        <v>42.35219593803296</v>
       </c>
       <c r="D9" t="n">
-        <v>1.92177674678482</v>
+        <v>1.9235490249325</v>
       </c>
       <c r="E9" t="n">
-        <v>9.983904971689146</v>
+        <v>10.02944558002369</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508540001939289</v>
+        <v>0.7508365542080615</v>
       </c>
       <c r="G9" t="n">
-        <v>29.68471655681239</v>
+        <v>29.72577064903728</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53928400892072</v>
+        <v>34.53848149357082</v>
       </c>
       <c r="I9" t="n">
-        <v>4.715356496682559</v>
+        <v>4.737214385423291</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692837501212056</v>
+        <v>4.692728463800384</v>
       </c>
       <c r="K9" t="n">
-        <v>13.71126971770436</v>
+        <v>13.60197384900398</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86757138129976</v>
+        <v>43.8882111425486</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84310723687459</v>
+        <v>99.84238092958553</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.18017945632802</v>
+        <v>84.32595187780191</v>
       </c>
       <c r="C10" t="n">
-        <v>40.88761207405193</v>
+        <v>41.01547397742733</v>
       </c>
       <c r="D10" t="n">
-        <v>1.827189530065246</v>
+        <v>1.830776014324651</v>
       </c>
       <c r="E10" t="n">
-        <v>10.14844209305566</v>
+        <v>10.20469892432427</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520241297794996</v>
+        <v>0.7520100537737975</v>
       </c>
       <c r="G10" t="n">
-        <v>28.22367550565188</v>
+        <v>28.2920930042232</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59310996985698</v>
+        <v>34.59246247359468</v>
       </c>
       <c r="I10" t="n">
-        <v>3.935587416796899</v>
+        <v>3.953848571475078</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700150811121873</v>
+        <v>4.700062836086234</v>
       </c>
       <c r="K10" t="n">
-        <v>15.81982054367196</v>
+        <v>15.67404812219808</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16158525736824</v>
+        <v>43.17888861189061</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86901787509214</v>
+        <v>99.86841071151602</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.96274502198034</v>
+        <v>82.1280169824863</v>
       </c>
       <c r="C11" t="n">
-        <v>39.28050618764861</v>
+        <v>39.43078873625737</v>
       </c>
       <c r="D11" t="n">
-        <v>1.728705654599542</v>
+        <v>1.733312924083426</v>
       </c>
       <c r="E11" t="n">
-        <v>10.14878957864243</v>
+        <v>10.21132312530778</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530285188815254</v>
+        <v>0.7530170573403205</v>
       </c>
       <c r="G11" t="n">
-        <v>26.70244473131408</v>
+        <v>26.7859367120233</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63931186855017</v>
+        <v>34.63878463765474</v>
       </c>
       <c r="I11" t="n">
-        <v>3.284036426983062</v>
+        <v>3.299285917699714</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706428243009535</v>
+        <v>4.706356608377003</v>
       </c>
       <c r="K11" t="n">
-        <v>18.03725497801965</v>
+        <v>17.87198301751372</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57291696164294</v>
+        <v>42.58739911924348</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8906781273112</v>
+        <v>99.89017087301457</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.6013722252651</v>
+        <v>79.82709897082691</v>
       </c>
       <c r="C12" t="n">
-        <v>37.42771185713661</v>
+        <v>37.64090596233153</v>
       </c>
       <c r="D12" t="n">
-        <v>1.624758275323558</v>
+        <v>1.632213616399099</v>
       </c>
       <c r="E12" t="n">
-        <v>9.995180531144863</v>
+        <v>10.07448597575582</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538924802464656</v>
+        <v>0.7538825647799567</v>
       </c>
       <c r="G12" t="n">
-        <v>25.09682196800745</v>
+        <v>25.22358774454315</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67905409133741</v>
+        <v>34.67859797987801</v>
       </c>
       <c r="I12" t="n">
-        <v>2.739836877664924</v>
+        <v>2.752565059596151</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711828001540411</v>
+        <v>4.711766029874729</v>
       </c>
       <c r="K12" t="n">
-        <v>20.39862777473492</v>
+        <v>20.1729010291731</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08243713404558</v>
+        <v>42.09454617744818</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90877676591712</v>
+        <v>99.9083531689528</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.18531003120184</v>
+        <v>77.51805224368835</v>
       </c>
       <c r="C13" t="n">
-        <v>35.43512396033477</v>
+        <v>35.75742387706117</v>
       </c>
       <c r="D13" t="n">
-        <v>1.519342893906231</v>
+        <v>1.531671089296543</v>
       </c>
       <c r="E13" t="n">
-        <v>9.727595154251333</v>
+        <v>9.836587103580509</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546365701312306</v>
+        <v>0.7546268930574568</v>
       </c>
       <c r="G13" t="n">
-        <v>23.46852371570688</v>
+        <v>23.66984304535095</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7132822260366</v>
+        <v>34.71283708064301</v>
       </c>
       <c r="I13" t="n">
-        <v>2.28545090784937</v>
+        <v>2.296068950150786</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716478563320193</v>
+        <v>4.716418081609104</v>
       </c>
       <c r="K13" t="n">
-        <v>22.81468996879817</v>
+        <v>22.48194775631164</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67407949093193</v>
+        <v>41.68416822608286</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92389342006486</v>
+        <v>99.92353985945567</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.71063592411902</v>
+        <v>84.02294950379401</v>
       </c>
       <c r="C14" t="n">
-        <v>39.52356497983061</v>
+        <v>39.76861539706382</v>
       </c>
       <c r="D14" t="n">
-        <v>1.52108382687021</v>
+        <v>1.533487933255949</v>
       </c>
       <c r="E14" t="n">
-        <v>12.00759586878161</v>
+        <v>12.0877235333449</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555012674197982</v>
+        <v>0.7555220195123707</v>
       </c>
       <c r="G14" t="n">
-        <v>25.28467193524224</v>
+        <v>25.43905481194937</v>
       </c>
       <c r="H14" t="n">
-        <v>36.54231520703109</v>
+        <v>36.49514787166447</v>
       </c>
       <c r="I14" t="n">
-        <v>2.877584897400336</v>
+        <v>2.990000712114632</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72188292137374</v>
+        <v>4.722012621952317</v>
       </c>
       <c r="K14" t="n">
-        <v>16.28936407588097</v>
+        <v>15.97705049620598</v>
       </c>
       <c r="L14" t="n">
-        <v>44.09126123088442</v>
+        <v>44.15478549930604</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90419028659599</v>
+        <v>99.90045139257583</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.99729804221329</v>
+        <v>83.40540074539166</v>
       </c>
       <c r="C15" t="n">
-        <v>39.2551795854915</v>
+        <v>39.61351741634281</v>
       </c>
       <c r="D15" t="n">
-        <v>1.494567711266682</v>
+        <v>1.510747666665792</v>
       </c>
       <c r="E15" t="n">
-        <v>12.19832470908872</v>
+        <v>12.32416513427405</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562295758700672</v>
+        <v>0.7562751226071284</v>
       </c>
       <c r="G15" t="n">
-        <v>24.84389985405347</v>
+        <v>25.06181618119141</v>
       </c>
       <c r="H15" t="n">
-        <v>36.57754225178321</v>
+        <v>36.53152617447493</v>
       </c>
       <c r="I15" t="n">
-        <v>2.400299090963225</v>
+        <v>2.494150949883808</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726434849187921</v>
+        <v>4.726719516294552</v>
       </c>
       <c r="K15" t="n">
-        <v>17.0027019577867</v>
+        <v>16.59459925460835</v>
       </c>
       <c r="L15" t="n">
-        <v>43.66218554290511</v>
+        <v>43.70882775371231</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92006708618332</v>
+        <v>99.91694442466346</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.63469273951222</v>
+        <v>81.24705787003616</v>
       </c>
       <c r="C16" t="n">
-        <v>37.26379142132275</v>
+        <v>37.84107108353344</v>
       </c>
       <c r="D16" t="n">
-        <v>1.40410009628266</v>
+        <v>1.428135517739964</v>
       </c>
       <c r="E16" t="n">
-        <v>11.79359919340557</v>
+        <v>11.99694884948905</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568554022125099</v>
+        <v>0.7569205730448078</v>
       </c>
       <c r="G16" t="n">
-        <v>23.34007480166207</v>
+        <v>23.69136197735888</v>
       </c>
       <c r="H16" t="n">
-        <v>36.60781241075793</v>
+        <v>36.56270436459855</v>
       </c>
       <c r="I16" t="n">
-        <v>2.001904571363293</v>
+        <v>2.080233006274866</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730346263828188</v>
+        <v>4.730753581530048</v>
       </c>
       <c r="K16" t="n">
-        <v>19.36530726048778</v>
+        <v>18.75294212996383</v>
       </c>
       <c r="L16" t="n">
-        <v>43.30422634344048</v>
+        <v>43.33670481567265</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93332502525101</v>
+        <v>99.93071802916992</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.2974493737639</v>
+        <v>82.85677067582739</v>
       </c>
       <c r="C17" t="n">
-        <v>38.47952987555404</v>
+        <v>39.02471098428451</v>
       </c>
       <c r="D17" t="n">
-        <v>1.405230828639823</v>
+        <v>1.429323643641756</v>
       </c>
       <c r="E17" t="n">
-        <v>12.56171084882713</v>
+        <v>12.75541064031942</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574649035545018</v>
+        <v>0.7575502870511206</v>
       </c>
       <c r="G17" t="n">
-        <v>23.78611114905514</v>
+        <v>24.11489270891042</v>
       </c>
       <c r="H17" t="n">
-        <v>37.06453336693399</v>
+        <v>36.99694330632423</v>
       </c>
       <c r="I17" t="n">
-        <v>1.988242629537685</v>
+        <v>2.067960795510952</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734155647215637</v>
+        <v>4.734689294069503</v>
       </c>
       <c r="K17" t="n">
-        <v>17.70255062623609</v>
+        <v>17.14322932417259</v>
       </c>
       <c r="L17" t="n">
-        <v>43.75169807250362</v>
+        <v>43.76318496480293</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93377857429375</v>
+        <v>99.93112527326004</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.04827520081152</v>
+        <v>80.81011141930705</v>
       </c>
       <c r="C18" t="n">
-        <v>36.5374883667822</v>
+        <v>37.29773480055665</v>
       </c>
       <c r="D18" t="n">
-        <v>1.322425261753826</v>
+        <v>1.353905720657747</v>
       </c>
       <c r="E18" t="n">
-        <v>12.09782658257624</v>
+        <v>12.36979551241128</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579878740161844</v>
+        <v>0.758089169931887</v>
       </c>
       <c r="G18" t="n">
-        <v>22.38447493558171</v>
+        <v>22.8424761158046</v>
       </c>
       <c r="H18" t="n">
-        <v>37.09012353756236</v>
+        <v>37.02326105674852</v>
       </c>
       <c r="I18" t="n">
-        <v>1.658012796720049</v>
+        <v>1.724526531678717</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737424212601153</v>
+        <v>4.738057312074294</v>
       </c>
       <c r="K18" t="n">
-        <v>19.95172479918848</v>
+        <v>19.18988858069296</v>
       </c>
       <c r="L18" t="n">
-        <v>43.4555578720977</v>
+        <v>43.45493326331952</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94477103806838</v>
+        <v>99.94255664456912</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.16792239945931</v>
+        <v>80.03208618116849</v>
       </c>
       <c r="C19" t="n">
-        <v>35.91264140767576</v>
+        <v>36.78575885451123</v>
       </c>
       <c r="D19" t="n">
-        <v>1.290660821356235</v>
+        <v>1.325892039013832</v>
       </c>
       <c r="E19" t="n">
-        <v>12.0376523474752</v>
+        <v>12.35351292943476</v>
       </c>
       <c r="F19" t="n">
-        <v>0.75842908987255</v>
+        <v>0.7585431988978315</v>
       </c>
       <c r="G19" t="n">
-        <v>21.84680347656884</v>
+        <v>22.36984213243093</v>
       </c>
       <c r="H19" t="n">
-        <v>37.11171326370484</v>
+        <v>37.04543474501661</v>
       </c>
       <c r="I19" t="n">
-        <v>1.382481588778225</v>
+        <v>1.437966143263078</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740181811703438</v>
+        <v>4.740894993111446</v>
       </c>
       <c r="K19" t="n">
-        <v>20.83207760054068</v>
+        <v>19.96791381883151</v>
       </c>
       <c r="L19" t="n">
-        <v>43.20922508076355</v>
+        <v>43.19842381188842</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95394408897999</v>
+        <v>99.95209648523115</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.70592495918029</v>
+        <v>77.81727317786475</v>
       </c>
       <c r="C20" t="n">
-        <v>33.66355962676856</v>
+        <v>34.79269481637124</v>
       </c>
       <c r="D20" t="n">
-        <v>1.200925365088951</v>
+        <v>1.245070264792096</v>
       </c>
       <c r="E20" t="n">
-        <v>11.39282097377119</v>
+        <v>11.80030576906405</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758808982099371</v>
+        <v>0.7589327580844335</v>
       </c>
       <c r="G20" t="n">
-        <v>20.32786616514448</v>
+        <v>21.00625424065361</v>
       </c>
       <c r="H20" t="n">
-        <v>37.13030228089992</v>
+        <v>37.0644598835289</v>
       </c>
       <c r="I20" t="n">
-        <v>1.152645054055319</v>
+        <v>1.198920523713941</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74255613812107</v>
+        <v>4.743329738027708</v>
       </c>
       <c r="K20" t="n">
-        <v>23.29407504081971</v>
+        <v>22.18272682213527</v>
       </c>
       <c r="L20" t="n">
-        <v>43.00396306605679</v>
+        <v>42.98463485751396</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96159773364505</v>
+        <v>99.96005649602046</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.22049998870507</v>
+        <v>83.09298899094622</v>
       </c>
       <c r="C21" t="n">
-        <v>37.10939959223671</v>
+        <v>38.02553592984067</v>
       </c>
       <c r="D21" t="n">
-        <v>1.201706791515588</v>
+        <v>1.245939513967685</v>
       </c>
       <c r="E21" t="n">
-        <v>13.24958829171591</v>
+        <v>13.56218189207878</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593027291785978</v>
+        <v>0.7594626090438109</v>
       </c>
       <c r="G21" t="n">
-        <v>21.92294838074037</v>
+        <v>22.48449954558941</v>
       </c>
       <c r="H21" t="n">
-        <v>38.73631762189594</v>
+        <v>38.55391626820151</v>
       </c>
       <c r="I21" t="n">
-        <v>1.604994116292428</v>
+        <v>1.740347855541206</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745642057366236</v>
+        <v>4.746641306523817</v>
       </c>
       <c r="K21" t="n">
-        <v>17.77950001129495</v>
+        <v>16.90701100905377</v>
       </c>
       <c r="L21" t="n">
-        <v>45.05763538157779</v>
+        <v>45.00948193861696</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94653498510945</v>
+        <v>99.9420288775114</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_90_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.42940953923235</v>
+        <v>45.70444404928644</v>
       </c>
       <c r="M2" t="n">
-        <v>98.9652998830841</v>
+        <v>99.40838195004079</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00920016343832</v>
+        <v>88.06050629846224</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88900246743617</v>
+        <v>45.93467827937626</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228714254844044</v>
+        <v>2.228811200529885</v>
       </c>
       <c r="E3" t="n">
-        <v>5.682813365944683</v>
+        <v>5.711620218446771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429047516146814</v>
+        <v>0.7429370668432952</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9595151024918</v>
+        <v>33.97485044826782</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17361857427534</v>
+        <v>34.17510507479157</v>
       </c>
       <c r="I3" t="n">
-        <v>6.578479416676012</v>
+        <v>6.583825621812314</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643154697591758</v>
+        <v>4.643356667770594</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99079983656169</v>
+        <v>11.93949370153775</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88406228645368</v>
+        <v>48.88951098621226</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7638645904515</v>
+        <v>106.7636829671263</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.15301538162967</v>
+        <v>87.20684752342729</v>
       </c>
       <c r="C4" t="n">
-        <v>42.67144038984712</v>
+        <v>42.71898038430453</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187728257673261</v>
+        <v>2.188007119933939</v>
       </c>
       <c r="E4" t="n">
-        <v>6.493904024940663</v>
+        <v>6.523396337785377</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444656883015559</v>
+        <v>0.7444983762869393</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33500050314974</v>
+        <v>33.3528540514457</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24542166187157</v>
+        <v>34.2469253091992</v>
       </c>
       <c r="I4" t="n">
-        <v>5.493584693808167</v>
+        <v>5.498051476982752</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652910551884724</v>
+        <v>4.65311485179337</v>
       </c>
       <c r="K4" t="n">
-        <v>12.84698461837034</v>
+        <v>12.7931524765727</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29883945243044</v>
+        <v>44.30498309407243</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81726446064789</v>
+        <v>99.81711595494967</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.08332369625988</v>
+        <v>86.09350360283345</v>
       </c>
       <c r="C5" t="n">
-        <v>42.45440466283544</v>
+        <v>42.45903022555017</v>
       </c>
       <c r="D5" t="n">
-        <v>2.135817548103723</v>
+        <v>2.133880966326178</v>
       </c>
       <c r="E5" t="n">
-        <v>7.104168638577063</v>
+        <v>7.126998116052204</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457877433484599</v>
+        <v>0.7458214095559287</v>
       </c>
       <c r="G5" t="n">
-        <v>32.54402313950778</v>
+        <v>32.52778283243602</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30623619402915</v>
+        <v>34.30778483957271</v>
       </c>
       <c r="I5" t="n">
-        <v>4.586117036765822</v>
+        <v>4.589851629165858</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661173395927873</v>
+        <v>4.661383809724554</v>
       </c>
       <c r="K5" t="n">
-        <v>13.91667630374014</v>
+        <v>13.90649639716654</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47631945859643</v>
+        <v>43.48174972514486</v>
       </c>
       <c r="M5" t="n">
-        <v>99.847400425172</v>
+        <v>99.84727634786157</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.81331790811886</v>
+        <v>84.80524742545549</v>
       </c>
       <c r="C6" t="n">
-        <v>41.89675198094682</v>
+        <v>41.88370653993204</v>
       </c>
       <c r="D6" t="n">
-        <v>2.074015587326144</v>
+        <v>2.071211775207229</v>
       </c>
       <c r="E6" t="n">
-        <v>7.536521473209894</v>
+        <v>7.556127063295974</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469096239405664</v>
+        <v>0.7469443628009546</v>
       </c>
       <c r="G6" t="n">
-        <v>31.60233013609642</v>
+        <v>31.57248594794709</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35784270126604</v>
+        <v>34.3594406888439</v>
       </c>
       <c r="I6" t="n">
-        <v>3.827513236651239</v>
+        <v>3.830635319854371</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668185149628539</v>
+        <v>4.668402267505965</v>
       </c>
       <c r="K6" t="n">
-        <v>15.18668209188114</v>
+        <v>15.19475257454453</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78917378726187</v>
+        <v>42.79404500693548</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87260786008984</v>
+        <v>99.87250412141204</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.33883516321038</v>
+        <v>83.34294514884171</v>
       </c>
       <c r="C7" t="n">
-        <v>41.01689313631054</v>
+        <v>41.0164995559506</v>
       </c>
       <c r="D7" t="n">
-        <v>2.002367556108172</v>
+        <v>2.000252196087487</v>
       </c>
       <c r="E7" t="n">
-        <v>7.808446230048879</v>
+        <v>7.829967461721425</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747863713704163</v>
+        <v>0.7478992290658243</v>
       </c>
       <c r="G7" t="n">
-        <v>30.51060992435451</v>
+        <v>30.49081465704005</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40173083039149</v>
+        <v>34.40336453702791</v>
       </c>
       <c r="I7" t="n">
-        <v>3.193668697952149</v>
+        <v>3.196276886237606</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674148210651018</v>
+        <v>4.674370181661401</v>
       </c>
       <c r="K7" t="n">
-        <v>16.66116483678963</v>
+        <v>16.65705485115829</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21562221477062</v>
+        <v>42.22003905622852</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89368018787079</v>
+        <v>99.89359346333741</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.23931996549028</v>
+        <v>88.19695820222039</v>
       </c>
       <c r="C8" t="n">
-        <v>43.31255300940229</v>
+        <v>43.30480841706066</v>
       </c>
       <c r="D8" t="n">
-        <v>2.006659674129188</v>
+        <v>2.004515046081438</v>
       </c>
       <c r="E8" t="n">
-        <v>9.639137992580386</v>
+        <v>9.653683426820399</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494667756959847</v>
+        <v>0.7494931191914469</v>
       </c>
       <c r="G8" t="n">
-        <v>31.01012995804944</v>
+        <v>30.98940613861481</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47547168201529</v>
+        <v>34.47668348280655</v>
       </c>
       <c r="I8" t="n">
-        <v>5.674286534920084</v>
+        <v>5.638844993759204</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684167348099904</v>
+        <v>4.684331994946542</v>
       </c>
       <c r="K8" t="n">
-        <v>11.7606800345097</v>
+        <v>11.8030417977796</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73802863624784</v>
+        <v>44.70458800882199</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81126168015984</v>
+        <v>99.81243822366224</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.398026150996</v>
+        <v>86.16403201495331</v>
       </c>
       <c r="C9" t="n">
-        <v>42.35219593803296</v>
+        <v>42.14734445924087</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9235490249325</v>
+        <v>1.912440373376757</v>
       </c>
       <c r="E9" t="n">
-        <v>10.02944558002369</v>
+        <v>9.994853817930903</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508365542080615</v>
+        <v>0.7508580778556007</v>
       </c>
       <c r="G9" t="n">
-        <v>29.72577064903728</v>
+        <v>29.56594991008547</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53848149357082</v>
+        <v>34.53947158135762</v>
       </c>
       <c r="I9" t="n">
-        <v>4.737214385423291</v>
+        <v>4.707595267749445</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692728463800384</v>
+        <v>4.692862986597503</v>
       </c>
       <c r="K9" t="n">
-        <v>13.60197384900398</v>
+        <v>13.83596798504671</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8882111425486</v>
+        <v>43.86005297255242</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84238092958553</v>
+        <v>99.84336541684</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.32595187780191</v>
+        <v>83.91702055788087</v>
       </c>
       <c r="C10" t="n">
-        <v>41.01547397742733</v>
+        <v>40.63092339825264</v>
       </c>
       <c r="D10" t="n">
-        <v>1.830776014324651</v>
+        <v>1.811647826226308</v>
       </c>
       <c r="E10" t="n">
-        <v>10.20469892432427</v>
+        <v>10.12294187754074</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520100537737975</v>
+        <v>0.7520299539637387</v>
       </c>
       <c r="G10" t="n">
-        <v>28.2920930042232</v>
+        <v>28.00771706693632</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59246247359468</v>
+        <v>34.59337788233198</v>
       </c>
       <c r="I10" t="n">
-        <v>3.953848571475078</v>
+        <v>3.929118738608421</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700062836086234</v>
+        <v>4.700187212273367</v>
       </c>
       <c r="K10" t="n">
-        <v>15.67404812219808</v>
+        <v>16.08297944211911</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17888861189061</v>
+        <v>43.155330624413</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86841071151602</v>
+        <v>99.86923346478476</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.1280169824863</v>
+        <v>81.47001219468237</v>
       </c>
       <c r="C11" t="n">
-        <v>39.43078873625737</v>
+        <v>38.79303929738644</v>
       </c>
       <c r="D11" t="n">
-        <v>1.733312924083426</v>
+        <v>1.70294117390102</v>
       </c>
       <c r="E11" t="n">
-        <v>10.21132312530778</v>
+        <v>10.06196486141798</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530170573403205</v>
+        <v>0.7530387705360739</v>
       </c>
       <c r="G11" t="n">
-        <v>26.7859367120233</v>
+        <v>26.32713372311806</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63878463765474</v>
+        <v>34.63978344465939</v>
       </c>
       <c r="I11" t="n">
-        <v>3.299285917699714</v>
+        <v>3.278657905199391</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706356608377003</v>
+        <v>4.706492315850461</v>
       </c>
       <c r="K11" t="n">
-        <v>17.87198301751372</v>
+        <v>18.52998780531762</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58739911924348</v>
+        <v>42.56783071011236</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89017087301457</v>
+        <v>99.89085781281642</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.82709897082691</v>
+        <v>78.85423860298627</v>
       </c>
       <c r="C12" t="n">
-        <v>37.64090596233153</v>
+        <v>36.68467409077694</v>
       </c>
       <c r="D12" t="n">
-        <v>1.632213616399099</v>
+        <v>1.587834398578181</v>
       </c>
       <c r="E12" t="n">
-        <v>10.07448597575582</v>
+        <v>9.837742920312543</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538825647799567</v>
+        <v>0.7539095091065288</v>
       </c>
       <c r="G12" t="n">
-        <v>25.22358774454315</v>
+        <v>24.54760574364046</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67859797987801</v>
+        <v>34.67983741890032</v>
       </c>
       <c r="I12" t="n">
-        <v>2.752565059596151</v>
+        <v>2.735374180532429</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711766029874729</v>
+        <v>4.711934431915804</v>
       </c>
       <c r="K12" t="n">
-        <v>20.1729010291731</v>
+        <v>21.14576139701373</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09454617744818</v>
+        <v>42.07849068150934</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9083531689528</v>
+        <v>99.90892616930002</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.51805224368835</v>
+        <v>76.31856929782245</v>
       </c>
       <c r="C13" t="n">
-        <v>35.75742387706117</v>
+        <v>34.57133634710343</v>
       </c>
       <c r="D13" t="n">
-        <v>1.531671089296543</v>
+        <v>1.477382378220982</v>
       </c>
       <c r="E13" t="n">
-        <v>9.836587103580509</v>
+        <v>9.533707221314181</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546268930574568</v>
+        <v>0.7546608479489955</v>
       </c>
       <c r="G13" t="n">
-        <v>23.66984304535095</v>
+        <v>22.84003935526588</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71283708064301</v>
+        <v>34.71439900565379</v>
       </c>
       <c r="I13" t="n">
-        <v>2.296068950150786</v>
+        <v>2.28175018973741</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716418081609104</v>
+        <v>4.716630299681221</v>
       </c>
       <c r="K13" t="n">
-        <v>22.48194775631164</v>
+        <v>23.68143070217752</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68416822608286</v>
+        <v>41.67125033459315</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92353985945567</v>
+        <v>99.92401738387412</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.02294950379401</v>
+        <v>83.15376899131616</v>
       </c>
       <c r="C14" t="n">
-        <v>39.76861539706382</v>
+        <v>38.85410831647306</v>
       </c>
       <c r="D14" t="n">
-        <v>1.533487933255949</v>
+        <v>1.479095263077051</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0877235333449</v>
+        <v>11.91240495620535</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555220195123707</v>
+        <v>0.7555358056830094</v>
       </c>
       <c r="G14" t="n">
-        <v>25.43905481194937</v>
+        <v>24.75211994789807</v>
       </c>
       <c r="H14" t="n">
-        <v>36.49514787166447</v>
+        <v>36.64024679296794</v>
       </c>
       <c r="I14" t="n">
-        <v>2.990000712114632</v>
+        <v>2.89226743996594</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722012621952317</v>
+        <v>4.722098785518807</v>
       </c>
       <c r="K14" t="n">
-        <v>15.97705049620598</v>
+        <v>16.84623100868384</v>
       </c>
       <c r="L14" t="n">
-        <v>44.15478549930604</v>
+        <v>44.20336340773267</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90045139257583</v>
+        <v>99.90370273288957</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.40540074539166</v>
+        <v>82.21051561455286</v>
       </c>
       <c r="C15" t="n">
-        <v>39.61351741634281</v>
+        <v>38.35760640720656</v>
       </c>
       <c r="D15" t="n">
-        <v>1.510747666665792</v>
+        <v>1.443929814140295</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32416513427405</v>
+        <v>12.031284620908</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562751226071284</v>
+        <v>0.7562748802390196</v>
       </c>
       <c r="G15" t="n">
-        <v>25.06181618119141</v>
+        <v>24.16363898130131</v>
       </c>
       <c r="H15" t="n">
-        <v>36.53152617447493</v>
+        <v>36.6760887397386</v>
       </c>
       <c r="I15" t="n">
-        <v>2.494150949883808</v>
+        <v>2.412580576731767</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726719516294552</v>
+        <v>4.726718001493871</v>
       </c>
       <c r="K15" t="n">
-        <v>16.59459925460835</v>
+        <v>17.78948438544714</v>
       </c>
       <c r="L15" t="n">
-        <v>43.70882775371231</v>
+        <v>43.77256844512503</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91694442466346</v>
+        <v>99.91965923777873</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.24705787003616</v>
+        <v>79.62365950124774</v>
       </c>
       <c r="C16" t="n">
-        <v>37.84107108353344</v>
+        <v>36.14335281894068</v>
       </c>
       <c r="D16" t="n">
-        <v>1.428135517739964</v>
+        <v>1.34582363455961</v>
       </c>
       <c r="E16" t="n">
-        <v>11.99694884948905</v>
+        <v>11.54919548021677</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569205730448078</v>
+        <v>0.7569119434856688</v>
       </c>
       <c r="G16" t="n">
-        <v>23.69136197735888</v>
+        <v>22.52186783563532</v>
       </c>
       <c r="H16" t="n">
-        <v>36.56270436459855</v>
+        <v>36.70698357543584</v>
       </c>
       <c r="I16" t="n">
-        <v>2.080233006274866</v>
+        <v>2.01217738512911</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730753581530048</v>
+        <v>4.730699646785428</v>
       </c>
       <c r="K16" t="n">
-        <v>18.75294212996383</v>
+        <v>20.37634049875227</v>
       </c>
       <c r="L16" t="n">
-        <v>43.33670481567265</v>
+        <v>43.41329055517561</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93071802916992</v>
+        <v>99.93298387286855</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.85677067582739</v>
+        <v>81.29535003960805</v>
       </c>
       <c r="C17" t="n">
-        <v>39.02471098428451</v>
+        <v>37.36156895199585</v>
       </c>
       <c r="D17" t="n">
-        <v>1.429323643641756</v>
+        <v>1.346929477373566</v>
       </c>
       <c r="E17" t="n">
-        <v>12.75541064031942</v>
+        <v>12.32005617593412</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575502870511206</v>
+        <v>0.7575338865189215</v>
       </c>
       <c r="G17" t="n">
-        <v>24.11489270891042</v>
+        <v>22.96774884520246</v>
       </c>
       <c r="H17" t="n">
-        <v>36.99694330632423</v>
+        <v>37.16452027888676</v>
       </c>
       <c r="I17" t="n">
-        <v>2.067960795510952</v>
+        <v>2.003974584948983</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734689294069503</v>
+        <v>4.734586790743258</v>
       </c>
       <c r="K17" t="n">
-        <v>17.14322932417259</v>
+        <v>18.70464996039193</v>
       </c>
       <c r="L17" t="n">
-        <v>43.76318496480293</v>
+        <v>43.86703677756516</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93112527326004</v>
+        <v>99.93325568995294</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.81011141930705</v>
+        <v>78.81928415472717</v>
       </c>
       <c r="C18" t="n">
-        <v>37.29773480055665</v>
+        <v>35.19453230361333</v>
       </c>
       <c r="D18" t="n">
-        <v>1.353905720657747</v>
+        <v>1.256780900606091</v>
       </c>
       <c r="E18" t="n">
-        <v>12.36979551241128</v>
+        <v>11.77401425412118</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758089169931887</v>
+        <v>0.7580692714151144</v>
       </c>
       <c r="G18" t="n">
-        <v>22.8424761158046</v>
+        <v>21.4305415119832</v>
       </c>
       <c r="H18" t="n">
-        <v>37.02326105674852</v>
+        <v>37.19078619673633</v>
       </c>
       <c r="I18" t="n">
-        <v>1.724526531678717</v>
+        <v>1.671159073520796</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738057312074294</v>
+        <v>4.737932946344463</v>
       </c>
       <c r="K18" t="n">
-        <v>19.18988858069296</v>
+        <v>21.18071584527281</v>
       </c>
       <c r="L18" t="n">
-        <v>43.45493326331952</v>
+        <v>43.56908589042084</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94255664456912</v>
+        <v>99.94433403930698</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.03208618116849</v>
+        <v>77.80644450068688</v>
       </c>
       <c r="C19" t="n">
-        <v>36.78575885451123</v>
+        <v>34.43072500871268</v>
       </c>
       <c r="D19" t="n">
-        <v>1.325892039013832</v>
+        <v>1.22023883321563</v>
       </c>
       <c r="E19" t="n">
-        <v>12.35351292943476</v>
+        <v>11.66520114708512</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585431988978315</v>
+        <v>0.758524323264508</v>
       </c>
       <c r="G19" t="n">
-        <v>22.36984213243093</v>
+        <v>20.80742869115078</v>
       </c>
       <c r="H19" t="n">
-        <v>37.04543474501661</v>
+        <v>37.21311098508666</v>
       </c>
       <c r="I19" t="n">
-        <v>1.437966143263078</v>
+        <v>1.401163500481021</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740894993111446</v>
+        <v>4.740777020403174</v>
       </c>
       <c r="K19" t="n">
-        <v>19.96791381883151</v>
+        <v>22.19355549931312</v>
       </c>
       <c r="L19" t="n">
-        <v>43.19842381188842</v>
+        <v>43.32904206136472</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95209648523115</v>
+        <v>99.95332256939052</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.81727317786475</v>
+        <v>75.15040462666346</v>
       </c>
       <c r="C20" t="n">
-        <v>34.79269481637124</v>
+        <v>31.9899591624261</v>
       </c>
       <c r="D20" t="n">
-        <v>1.245070264792096</v>
+        <v>1.12462873935585</v>
       </c>
       <c r="E20" t="n">
-        <v>11.80030576906405</v>
+        <v>10.94589763574894</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589327580844335</v>
+        <v>0.7589173747910953</v>
       </c>
       <c r="G20" t="n">
-        <v>21.00625424065361</v>
+        <v>19.17709194395922</v>
       </c>
       <c r="H20" t="n">
-        <v>37.0644598835289</v>
+        <v>37.2323940451457</v>
       </c>
       <c r="I20" t="n">
-        <v>1.198920523713941</v>
+        <v>1.168241295218324</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743329738027708</v>
+        <v>4.743233592444344</v>
       </c>
       <c r="K20" t="n">
-        <v>22.18272682213527</v>
+        <v>24.84959537333653</v>
       </c>
       <c r="L20" t="n">
-        <v>42.98463485751396</v>
+        <v>43.12152425589068</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96005649602046</v>
+        <v>99.96107879165331</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.09298899094622</v>
+        <v>81.20127897458714</v>
       </c>
       <c r="C21" t="n">
-        <v>38.02553592984067</v>
+        <v>35.80512493013924</v>
       </c>
       <c r="D21" t="n">
-        <v>1.245939513967685</v>
+        <v>1.125368484991096</v>
       </c>
       <c r="E21" t="n">
-        <v>13.56218189207878</v>
+        <v>12.9871705784354</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594626090438109</v>
+        <v>0.7594165669207891</v>
       </c>
       <c r="G21" t="n">
-        <v>22.48449954558941</v>
+        <v>20.95672079190629</v>
       </c>
       <c r="H21" t="n">
-        <v>38.55391626820151</v>
+        <v>39.02389910650881</v>
       </c>
       <c r="I21" t="n">
-        <v>1.740347855541206</v>
+        <v>1.60234990256983</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746641306523817</v>
+        <v>4.74635354325493</v>
       </c>
       <c r="K21" t="n">
-        <v>16.90701100905377</v>
+        <v>18.79872102541286</v>
       </c>
       <c r="L21" t="n">
-        <v>45.00948193861696</v>
+        <v>45.34277749045786</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9420288775114</v>
+        <v>99.94662344600997</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_90_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.70444404928644</v>
+        <v>43.52385703190279</v>
       </c>
       <c r="M2" t="n">
-        <v>99.40838195004079</v>
+        <v>97.02832597639639</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06050629846224</v>
+        <v>81.54793959265922</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93467827937626</v>
+        <v>43.30349514821479</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228811200529885</v>
+        <v>2.183573677947997</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711620218446771</v>
+        <v>4.164475223269527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429370668432952</v>
+        <v>0.7376830760924339</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97485044826782</v>
+        <v>32.84458740580113</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17510507479157</v>
+        <v>33.93342150025195</v>
       </c>
       <c r="I3" t="n">
-        <v>6.583825621812314</v>
+        <v>3.073679483718474</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643356667770594</v>
+        <v>4.610519225577711</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93949370153775</v>
+        <v>18.45206040734077</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88951098621226</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636829671263</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.20684752342729</v>
+        <v>88.74701886432365</v>
       </c>
       <c r="C4" t="n">
-        <v>42.71898038430453</v>
+        <v>42.89397778185837</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188007119933939</v>
+        <v>2.189390310768196</v>
       </c>
       <c r="E4" t="n">
-        <v>6.523396337785377</v>
+        <v>6.550613125864426</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444983762869393</v>
+        <v>0.7396481261544663</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3528540514457</v>
+        <v>33.52858777180683</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2469253091992</v>
+        <v>34.02381380310545</v>
       </c>
       <c r="I4" t="n">
-        <v>5.498051476982752</v>
+        <v>7.09216493815887</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65311485179337</v>
+        <v>4.622800788465414</v>
       </c>
       <c r="K4" t="n">
-        <v>12.7931524765727</v>
+        <v>11.25298113567635</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30498309407243</v>
+        <v>45.61726365160607</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81711595494967</v>
+        <v>99.76422256914078</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.09350360283345</v>
+        <v>87.9040606639048</v>
       </c>
       <c r="C5" t="n">
-        <v>42.45903022555017</v>
+        <v>43.15030404225268</v>
       </c>
       <c r="D5" t="n">
-        <v>2.133880966326178</v>
+        <v>2.150547182834717</v>
       </c>
       <c r="E5" t="n">
-        <v>7.126998116052204</v>
+        <v>7.421630677120141</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458214095559287</v>
+        <v>0.7413094984105258</v>
       </c>
       <c r="G5" t="n">
-        <v>32.52778283243602</v>
+        <v>32.93373941706456</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30778483957271</v>
+        <v>34.10023692688419</v>
       </c>
       <c r="I5" t="n">
-        <v>4.589851629165858</v>
+        <v>5.923412596524883</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661383809724554</v>
+        <v>4.633184365065786</v>
       </c>
       <c r="K5" t="n">
-        <v>13.90649639716654</v>
+        <v>12.09593933609521</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48174972514486</v>
+        <v>44.55675204003659</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84727634786157</v>
+        <v>99.80299541838447</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.80524742545549</v>
+        <v>86.89236080695856</v>
       </c>
       <c r="C6" t="n">
-        <v>41.88370653993204</v>
+        <v>43.0582231124455</v>
       </c>
       <c r="D6" t="n">
-        <v>2.071211775207229</v>
+        <v>2.103344062564128</v>
       </c>
       <c r="E6" t="n">
-        <v>7.556127063295974</v>
+        <v>8.0829876878033</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469443628009546</v>
+        <v>0.7427159040871879</v>
       </c>
       <c r="G6" t="n">
-        <v>31.57248594794709</v>
+        <v>32.21086512950079</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3594406888439</v>
+        <v>34.16493158801065</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830635319854371</v>
+        <v>4.945542034447588</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668402267505965</v>
+        <v>4.641974400544924</v>
       </c>
       <c r="K6" t="n">
-        <v>15.19475257454453</v>
+        <v>13.10763919304145</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79404500693548</v>
+        <v>43.66959845572071</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87250412141204</v>
+        <v>99.83546076120766</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.34294514884171</v>
+        <v>85.63557095418095</v>
       </c>
       <c r="C7" t="n">
-        <v>41.0164995559506</v>
+        <v>42.5700037692955</v>
       </c>
       <c r="D7" t="n">
-        <v>2.000252196087487</v>
+        <v>2.044273564769194</v>
       </c>
       <c r="E7" t="n">
-        <v>7.829967461721425</v>
+        <v>8.543968857294386</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478992290658243</v>
+        <v>0.7439092797460689</v>
       </c>
       <c r="G7" t="n">
-        <v>30.49081465704005</v>
+        <v>31.30625238854696</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40336453702791</v>
+        <v>34.21982686831917</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196276886237606</v>
+        <v>4.127906997092221</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674370181661401</v>
+        <v>4.64943299841293</v>
       </c>
       <c r="K7" t="n">
-        <v>16.65705485115829</v>
+        <v>14.36442904581907</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22003905622852</v>
+        <v>42.9281910172619</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89359346333741</v>
+        <v>99.86262383237647</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.19695820222039</v>
+        <v>84.16183288236061</v>
       </c>
       <c r="C8" t="n">
-        <v>43.30480841706066</v>
+        <v>41.73798643479908</v>
       </c>
       <c r="D8" t="n">
-        <v>2.004515046081438</v>
+        <v>1.975052258949137</v>
       </c>
       <c r="E8" t="n">
-        <v>9.653683426820399</v>
+        <v>8.828763452058153</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494931191914469</v>
+        <v>0.7449241821729318</v>
       </c>
       <c r="G8" t="n">
-        <v>30.98940613861481</v>
+        <v>30.24618894693407</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47668348280655</v>
+        <v>34.26651237995486</v>
       </c>
       <c r="I8" t="n">
-        <v>5.638844993759204</v>
+        <v>3.444615523710632</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684331994946542</v>
+        <v>4.655776138580823</v>
       </c>
       <c r="K8" t="n">
-        <v>11.8030417977796</v>
+        <v>15.8381671176394</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70458800882199</v>
+        <v>42.30918236430895</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81243822366224</v>
+        <v>99.88533591674744</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.16403201495331</v>
+        <v>82.5441311142705</v>
       </c>
       <c r="C9" t="n">
-        <v>42.14734445924087</v>
+        <v>40.65564589476176</v>
       </c>
       <c r="D9" t="n">
-        <v>1.912440373376757</v>
+        <v>1.899421023123341</v>
       </c>
       <c r="E9" t="n">
-        <v>9.994853817930903</v>
+        <v>8.969655152734719</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508580778556007</v>
+        <v>0.7457886878409458</v>
       </c>
       <c r="G9" t="n">
-        <v>29.56594991008547</v>
+        <v>29.08796306267605</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53947158135762</v>
+        <v>34.30627964068351</v>
       </c>
       <c r="I9" t="n">
-        <v>4.707595267749445</v>
+        <v>2.87384424820602</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692862986597503</v>
+        <v>4.66117929900591</v>
       </c>
       <c r="K9" t="n">
-        <v>13.83596798504671</v>
+        <v>17.45586888572952</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86005297255242</v>
+        <v>41.79280145496121</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84336541684</v>
+        <v>99.90431623545248</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.91702055788087</v>
+        <v>86.64038705808646</v>
       </c>
       <c r="C10" t="n">
-        <v>40.63092339825264</v>
+        <v>43.533466389452</v>
       </c>
       <c r="D10" t="n">
-        <v>1.811647826226308</v>
+        <v>1.901518828565216</v>
       </c>
       <c r="E10" t="n">
-        <v>10.12294187754074</v>
+        <v>10.63566780012029</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520299539637387</v>
+        <v>0.7466123701887746</v>
       </c>
       <c r="G10" t="n">
-        <v>28.00771706693632</v>
+        <v>30.29774769588323</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59337788233198</v>
+        <v>35.5218276158678</v>
       </c>
       <c r="I10" t="n">
-        <v>3.929118738608421</v>
+        <v>2.870685433781305</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700187212273367</v>
+        <v>4.66632731367984</v>
       </c>
       <c r="K10" t="n">
-        <v>16.08297944211911</v>
+        <v>13.35961294191355</v>
       </c>
       <c r="L10" t="n">
-        <v>43.155330624413</v>
+        <v>43.01133672135703</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86923346478476</v>
+        <v>99.90441605272258</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.47001219468237</v>
+        <v>86.52440338430671</v>
       </c>
       <c r="C11" t="n">
-        <v>38.79303929738644</v>
+        <v>43.78228767105898</v>
       </c>
       <c r="D11" t="n">
-        <v>1.70294117390102</v>
+        <v>1.892117403184381</v>
       </c>
       <c r="E11" t="n">
-        <v>10.06196486141798</v>
+        <v>11.01404181855849</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530387705360739</v>
+        <v>0.7473177564559765</v>
       </c>
       <c r="G11" t="n">
-        <v>26.32713372311806</v>
+        <v>30.17017543004235</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63978344465939</v>
+        <v>35.57761285372452</v>
       </c>
       <c r="I11" t="n">
-        <v>3.278657905199391</v>
+        <v>2.452402144491146</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706492315850461</v>
+        <v>4.670735977849852</v>
       </c>
       <c r="K11" t="n">
-        <v>18.52998780531762</v>
+        <v>13.47559661569327</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56783071011236</v>
+        <v>42.66044613508252</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89085781281642</v>
+        <v>99.91833042183478</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.85423860298627</v>
+        <v>84.8571994329548</v>
       </c>
       <c r="C12" t="n">
-        <v>36.68467409077694</v>
+        <v>42.49705986584637</v>
       </c>
       <c r="D12" t="n">
-        <v>1.587834398578181</v>
+        <v>1.820347231372663</v>
       </c>
       <c r="E12" t="n">
-        <v>9.837742920312543</v>
+        <v>10.9371517136646</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539095091065288</v>
+        <v>0.7479181756668412</v>
       </c>
       <c r="G12" t="n">
-        <v>24.54760574364046</v>
+        <v>29.02578625495224</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67983741890032</v>
+        <v>35.6061970564275</v>
       </c>
       <c r="I12" t="n">
-        <v>2.735374180532429</v>
+        <v>2.045310402953202</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711934431915804</v>
+        <v>4.674488597917756</v>
       </c>
       <c r="K12" t="n">
-        <v>21.14576139701373</v>
+        <v>15.1428005670452</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07849068150934</v>
+        <v>42.29201728531699</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90892616930002</v>
+        <v>99.93187771820855</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.31856929782245</v>
+        <v>85.90753203182031</v>
       </c>
       <c r="C13" t="n">
-        <v>34.57133634710343</v>
+        <v>43.40782036369986</v>
       </c>
       <c r="D13" t="n">
-        <v>1.477382378220982</v>
+        <v>1.821672149821937</v>
       </c>
       <c r="E13" t="n">
-        <v>9.533707221314181</v>
+        <v>11.54005668534491</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546608479489955</v>
+        <v>0.7484625391665131</v>
       </c>
       <c r="G13" t="n">
-        <v>22.84003935526588</v>
+        <v>29.32922286390398</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71439900565379</v>
+        <v>35.91442314044445</v>
       </c>
       <c r="I13" t="n">
-        <v>2.28175018973741</v>
+        <v>1.875803783347816</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716630299681221</v>
+        <v>4.677890869790706</v>
       </c>
       <c r="K13" t="n">
-        <v>23.68143070217752</v>
+        <v>14.09246796817971</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67125033459315</v>
+        <v>42.43723035163787</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92401738387412</v>
+        <v>99.93751868351742</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.15376899131616</v>
+        <v>84.13262053983546</v>
       </c>
       <c r="C14" t="n">
-        <v>38.85410831647306</v>
+        <v>41.92503104949523</v>
       </c>
       <c r="D14" t="n">
-        <v>1.479095263077051</v>
+        <v>1.747016604971164</v>
       </c>
       <c r="E14" t="n">
-        <v>11.91240495620535</v>
+        <v>11.32781325179042</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555358056830094</v>
+        <v>0.7489263699973542</v>
       </c>
       <c r="G14" t="n">
-        <v>24.75211994789807</v>
+        <v>28.12725624594337</v>
       </c>
       <c r="H14" t="n">
-        <v>36.64024679296794</v>
+        <v>35.93667972090466</v>
       </c>
       <c r="I14" t="n">
-        <v>2.89226743996594</v>
+        <v>1.564138533745022</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722098785518807</v>
+        <v>4.680789812483463</v>
       </c>
       <c r="K14" t="n">
-        <v>16.84623100868384</v>
+        <v>15.86737946016456</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20336340773267</v>
+        <v>42.15548382969167</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90370273288957</v>
+        <v>99.94789433935145</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.21051561455286</v>
+        <v>83.34170495434013</v>
       </c>
       <c r="C15" t="n">
-        <v>38.35760640720656</v>
+        <v>41.35747159460092</v>
       </c>
       <c r="D15" t="n">
-        <v>1.443929814140295</v>
+        <v>1.713409041438179</v>
       </c>
       <c r="E15" t="n">
-        <v>12.031284620908</v>
+        <v>11.33046123803185</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562748802390196</v>
+        <v>0.7493227742762717</v>
       </c>
       <c r="G15" t="n">
-        <v>24.16363898130131</v>
+        <v>27.58616891534546</v>
       </c>
       <c r="H15" t="n">
-        <v>36.6760887397386</v>
+        <v>35.95570088798081</v>
       </c>
       <c r="I15" t="n">
-        <v>2.412580576731767</v>
+        <v>1.323374758040859</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726718001493871</v>
+        <v>4.683267339226697</v>
       </c>
       <c r="K15" t="n">
-        <v>17.78948438544714</v>
+        <v>16.65829504565988</v>
       </c>
       <c r="L15" t="n">
-        <v>43.77256844512503</v>
+        <v>41.94014420405047</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91965923777873</v>
+        <v>99.95591084431126</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.62365950124774</v>
+        <v>81.07461388578523</v>
       </c>
       <c r="C16" t="n">
-        <v>36.14335281894068</v>
+        <v>39.29607295026476</v>
       </c>
       <c r="D16" t="n">
-        <v>1.34582363455961</v>
+        <v>1.618537431466927</v>
       </c>
       <c r="E16" t="n">
-        <v>11.54919548021677</v>
+        <v>10.88697802450958</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569119434856688</v>
+        <v>0.7496626822474541</v>
       </c>
       <c r="G16" t="n">
-        <v>22.52186783563532</v>
+        <v>26.05872030579395</v>
       </c>
       <c r="H16" t="n">
-        <v>36.70698357543584</v>
+        <v>35.972011121382</v>
       </c>
       <c r="I16" t="n">
-        <v>2.01217738512911</v>
+        <v>1.103312556338716</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730699646785428</v>
+        <v>4.685391764046588</v>
       </c>
       <c r="K16" t="n">
-        <v>20.37634049875227</v>
+        <v>18.92538611421478</v>
       </c>
       <c r="L16" t="n">
-        <v>43.41329055517561</v>
+        <v>41.74178052557489</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93298387286855</v>
+        <v>99.96323959005443</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.29535003960805</v>
+        <v>85.13353195926916</v>
       </c>
       <c r="C17" t="n">
-        <v>37.36156895199585</v>
+        <v>41.980559865754</v>
       </c>
       <c r="D17" t="n">
-        <v>1.346929477373566</v>
+        <v>1.619313107863923</v>
       </c>
       <c r="E17" t="n">
-        <v>12.32005617593412</v>
+        <v>12.3281648652331</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575338865189215</v>
+        <v>0.7500219545367585</v>
       </c>
       <c r="G17" t="n">
-        <v>22.96774884520246</v>
+        <v>27.30317892257337</v>
       </c>
       <c r="H17" t="n">
-        <v>37.16452027888676</v>
+        <v>37.2212206358254</v>
       </c>
       <c r="I17" t="n">
-        <v>2.003974584948983</v>
+        <v>1.223995257381868</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734586790743258</v>
+        <v>4.68763721585474</v>
       </c>
       <c r="K17" t="n">
-        <v>18.70464996039193</v>
+        <v>14.86646804073086</v>
       </c>
       <c r="L17" t="n">
-        <v>43.86703677756516</v>
+        <v>43.11219179536714</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93325568995294</v>
+        <v>99.95921970185198</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.81928415472717</v>
+        <v>86.57688761657579</v>
       </c>
       <c r="C18" t="n">
-        <v>35.19453230361333</v>
+        <v>42.67233483774164</v>
       </c>
       <c r="D18" t="n">
-        <v>1.256780900606091</v>
+        <v>1.620518100455077</v>
       </c>
       <c r="E18" t="n">
-        <v>11.77401425412118</v>
+        <v>12.89281785287493</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580692714151144</v>
+        <v>0.7505800744544143</v>
       </c>
       <c r="G18" t="n">
-        <v>21.4305415119832</v>
+        <v>27.44017292043594</v>
       </c>
       <c r="H18" t="n">
-        <v>37.19078619673633</v>
+        <v>37.24891836449942</v>
       </c>
       <c r="I18" t="n">
-        <v>1.671159073520796</v>
+        <v>1.932754838515898</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737932946344463</v>
+        <v>4.69112546534009</v>
       </c>
       <c r="K18" t="n">
-        <v>21.18071584527281</v>
+        <v>13.42311238342424</v>
       </c>
       <c r="L18" t="n">
-        <v>43.56908589042084</v>
+        <v>43.84017552311948</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94433403930698</v>
+        <v>99.93562274428537</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.80644450068688</v>
+        <v>84.07358805037906</v>
       </c>
       <c r="C19" t="n">
-        <v>34.43072500871268</v>
+        <v>40.46922755403978</v>
       </c>
       <c r="D19" t="n">
-        <v>1.22023883321563</v>
+        <v>1.52479805079445</v>
       </c>
       <c r="E19" t="n">
-        <v>11.66520114708512</v>
+        <v>12.39988026506444</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758524323264508</v>
+        <v>0.7510596854564285</v>
       </c>
       <c r="G19" t="n">
-        <v>20.80742869115078</v>
+        <v>25.81934886799078</v>
       </c>
       <c r="H19" t="n">
-        <v>37.21311098508666</v>
+        <v>37.27271994366301</v>
       </c>
       <c r="I19" t="n">
-        <v>1.401163500481021</v>
+        <v>1.611658203307286</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740777020403174</v>
+        <v>4.694123034102678</v>
       </c>
       <c r="K19" t="n">
-        <v>22.19355549931312</v>
+        <v>15.92641194962092</v>
       </c>
       <c r="L19" t="n">
-        <v>43.32904206136472</v>
+        <v>43.55067286193609</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95332256939052</v>
+        <v>99.9463123655968</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.15040462666346</v>
+        <v>81.49390851279199</v>
       </c>
       <c r="C20" t="n">
-        <v>31.9899591624261</v>
+        <v>38.13924874884502</v>
       </c>
       <c r="D20" t="n">
-        <v>1.12462873935585</v>
+        <v>1.426611149848114</v>
       </c>
       <c r="E20" t="n">
-        <v>10.94589763574894</v>
+        <v>11.82537450892212</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589173747910953</v>
+        <v>0.7514725032317062</v>
       </c>
       <c r="G20" t="n">
-        <v>19.17709194395922</v>
+        <v>24.15675371417389</v>
       </c>
       <c r="H20" t="n">
-        <v>37.2323940451457</v>
+        <v>37.29320678595217</v>
       </c>
       <c r="I20" t="n">
-        <v>1.168241295218324</v>
+        <v>1.343786705465835</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743233592444344</v>
+        <v>4.696703145198163</v>
       </c>
       <c r="K20" t="n">
-        <v>24.84959537333653</v>
+        <v>18.50609148720801</v>
       </c>
       <c r="L20" t="n">
-        <v>43.12152425589068</v>
+        <v>43.30989148052176</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96107879165331</v>
+        <v>99.95523171657479</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.20127897458714</v>
+        <v>78.76615196897335</v>
       </c>
       <c r="C21" t="n">
-        <v>35.80512493013924</v>
+        <v>35.61909237478301</v>
       </c>
       <c r="D21" t="n">
-        <v>1.125368484991096</v>
+        <v>1.323213121502653</v>
       </c>
       <c r="E21" t="n">
-        <v>12.9871705784354</v>
+        <v>11.15501967332895</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594165669207891</v>
+        <v>0.751828796130147</v>
       </c>
       <c r="G21" t="n">
-        <v>20.95672079190629</v>
+        <v>22.40591873329041</v>
       </c>
       <c r="H21" t="n">
-        <v>39.02389910650881</v>
+        <v>37.31088847713951</v>
       </c>
       <c r="I21" t="n">
-        <v>1.60234990256983</v>
+        <v>1.120353191768264</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74635354325493</v>
+        <v>4.698929975813417</v>
       </c>
       <c r="K21" t="n">
-        <v>18.79872102541286</v>
+        <v>21.23384803102665</v>
       </c>
       <c r="L21" t="n">
-        <v>45.34277749045786</v>
+        <v>43.1097321857052</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94662344600997</v>
+        <v>99.96267259151486</v>
       </c>
     </row>
   </sheetData>
